--- a/DesignDocs/Rules.xlsx
+++ b/DesignDocs/Rules.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cstewa01\source\repos\happysulla\TheyveInvadedPleasantville\DesignDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{091A0E54-08F3-4336-82B2-3516D8101600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{83078706-A016-4162-A96C-6AAB2A4FF58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="90" windowWidth="29040" windowHeight="15510" xr2:uid="{89590866-6083-4176-8CBF-8C95C9BA24C2}"/>
+    <workbookView xWindow="28680" yWindow="90" windowWidth="29040" windowHeight="16230" xr2:uid="{89590866-6083-4176-8CBF-8C95C9BA24C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Rules" sheetId="1" r:id="rId1"/>
@@ -498,13 +498,6 @@
                             &lt;InlineUIContainer&gt;&lt;Image Name='ZebulonBlack'  Height='150' Width='150'&gt;&lt;/Image&gt;&lt;/InlineUIContainer&gt;</t>
   </si>
   <si>
-    <t>&lt;Bold&gt;r7.0 Conversation and Influence (Town player only)&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-Conversation and Influence are methods where the Town player interacts with uncontrolled counters to either determine if townsperson is Alien controlled or a way for Town player to recruit additional Town controlled counters.
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-&lt;InlineUIContainer&gt;&lt;Button Content='r7.1' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Conversation&lt;LineBreak/&gt;
-&lt;InlineUIContainer&gt;&lt;Button Content='r7.2' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Influence&lt;LineBreak/&gt;</t>
-  </si>
-  <si>
     <t>&lt;Bold&gt;r8.7.1  Combat - Post Combat Activity - Tie Up&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
 Town controlled counters may always tie up knocked-out or surrendering Alien controlled counters.
 &lt;LineBreak/&gt;&lt;LineBreak/&gt;
@@ -539,22 +532,6 @@
 A townsperson may be talked to more than once a turn if there is a more than one Town controlled piece in that space, provided each Town controlled piece only makes one attempt at conversation each turn. </t>
   </si>
   <si>
-    <t>&lt;Bold&gt;r7.2 Influence&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-The Town player may also try to influence uncontrolled townsperson counters during this phase. 
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-Influencing is trying to convince other townspeople that there is an alien plot afoot to take-over Pleasantville. 
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-This is how the Town player can gain control of additional townspeople. Alien controlled counters cannot influence other counters but take-over townspeople per 
-&lt;InlineUIContainer&gt;&lt;Button Content='r9.1' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt;.
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-&lt;InlineUIContainer&gt;&lt;Button Content='r7.2.1' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Process&lt;LineBreak/&gt;
-&lt;InlineUIContainer&gt;&lt;Button Content='r7.2.2' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Mutliple Town Controlled Counters&lt;LineBreak/&gt;
-&lt;InlineUIContainer&gt;&lt;Button Content='r7.2.3' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Rolling&lt;LineBreak/&gt;
-&lt;InlineUIContainer&gt;&lt;Button Content='r7.2.4' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; No Effect Result&lt;LineBreak/&gt;
-&lt;InlineUIContainer&gt;&lt;Button Content='r7.2.5' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Convinced Result&lt;LineBreak/&gt;
-&lt;InlineUIContainer&gt;&lt;Button Content='r7.2.6' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Alien Controlled Counters</t>
-  </si>
-  <si>
     <t>&lt;Bold&gt;r7.2.2 Influence - Mutliple Town Controlled Counters&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
 When a stack of Town controlled pieces is attempting to influence the same counter, all the Influence Factors of the Town controlled counters are added together. 
 &lt;LineBreak/&gt;&lt;LineBreak/&gt;
@@ -563,22 +540,6 @@
 If there is more than one uncontrolled townsperson in the same space and only one Town controlled piece, the Town player can only attempt to influence one of them. 
 &lt;LineBreak/&gt;&lt;LineBreak/&gt;
 If there are more than one Town controlled counter in that same space, each Town controlled counter could try to influence a different uncontrolled counter, or they can combined to influence one uncontrolled piece.</t>
-  </si>
-  <si>
-    <t>&lt;Bold&gt;r9.2.1 Observation Example&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-If the observation attempt is successful, the Town player may flip over one of the observed counters to see if it is Alien controlled. If an Alien controlled counter is discovered, and the observing townsperson is currently uncontrolled, the counter has observed a take-over. 
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-The observing counter is still uncontrolled but wary.
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-A town player who tries to influence a wary person gains a +1 on his or her dice roll on the 
-&lt;InlineUIContainer&gt;&lt;Button Content='Influence Result' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt; &lt;/InlineUIContainer&gt; Table per 
-&lt;InlineUIContainer&gt;&lt;Button Content='r7.2.3' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; because that townsperson has already witnessed some funny business which makes this suspicious.
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-In addition, that townsperson is now somewhat alert to a take-over attempt, lest the same thing happen to him or her, and may not be moved or taken-over outright by the Alien player for the remainder of the game. This counter must be attacked and defeated by the Alien player before the Alien player moves it or tries to take-over it again per Combat per 
-&lt;InlineUIContainer&gt;&lt;Button Content='r7.2.3' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt;.. 
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-If the Alien player is defeated in an attack on the wary townsperson, the result is an automatic flee result for the Alien controlled counters involved per 
-&lt;InlineUIContainer&gt;&lt;Button Content='r8.6' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt;.</t>
   </si>
   <si>
     <t>&lt;Bold&gt;r8.2 Combat - Attacking Uncontrolled Townspeople&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
@@ -611,17 +572,6 @@
 An Alien controlled counter may only take-over one townsperson per turn. If there is more than one Alien controlled counter in the same space and more than one uncontrolled counter, each Alien controlled counter may take-over an uncontrolled counter. 
 &lt;LineBreak/&gt;&lt;LineBreak/&gt;
 An uncontrolled townsperson who has successfully observed an Alien takeover is not subject to take-over as explained in Observation section per &lt;InlineUIContainer&gt;&lt;Button Content='r9.2' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt;. Observation only applies if the uncontrolled counter is also not being taken-over in the same turn in the same area. Observation roll occurs whenever the take-over chance (when counters are removed from board) to do a possible take-over.</t>
-  </si>
-  <si>
-    <t>&lt;Bold&gt;r9.2 Take-over Observation&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-There is a chance that a nearby townsperson will watch closely enough to detect an Alien take-over if one occurs. 
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-Any time the Alien player removes counters from the mapboard during a take-over, a townsperson might notice or observe the take-over. 
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-Refer to the &lt;InlineUIContainer&gt;&lt;Button Content='Observation' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Table which gives the number that must be rolled on one die for a townsperson to successfully observe a take-over based on the townsperson location to the observation space.
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-&lt;InlineUIContainer&gt;&lt;Button Content='r9.2.1' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Observation Example&lt;LineBreak/&gt;
-&lt;InlineUIContainer&gt;&lt;Button Content='r9.2.2' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Observation Restrictions&lt;LineBreak/&gt;</t>
   </si>
   <si>
     <t>&lt;Bold&gt;r3.3 Roll for Alien Controlled Counter&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
@@ -694,7 +644,111 @@
 &lt;InlineUIContainer&gt;&lt;Button Content='r6.3.3' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Limitations</t>
   </si>
   <si>
-    <t>&lt;Bold&gt;r8.0 Combat&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+    <t>&lt;Bold&gt;r8.7 Combat - Post Combat Activity&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+The Town player after winning a combat may choose to do one of the following actions with the defeated Alien controlled counters. These actions are purely voluntary on the part of the Town player, though they can be crucial to the Town player's chances of victory. 
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+Depending on the actual result inflicted upon a defeated Alien controlled counter, some actions may not always be possible (e.g., interrogating a dead or knocked-out piece). The  &lt;InlineUIContainer&gt;&lt;Button Content='Alien Loss' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Table specifies which actions may be taken in each given circumstances.
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+Post Combat Activities are the following:&lt;LineBreak/&gt;
+&lt;InlineUIContainer&gt;&lt;Button Content='r8.7.1' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Tie Up&lt;LineBreak/&gt;
+&lt;InlineUIContainer&gt;&lt;Button Content='r8.7.2' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Interrogation&lt;LineBreak/&gt;
+&lt;InlineUIContainer&gt;&lt;Button Content='r8.7.3' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Implant Removal&lt;LineBreak/&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Bold&gt;r9.2.2 Observation Restrictions&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+Observation cannot take place more than 3 spaces away. Observations are blocked by corners and walls. Townspeople have no chance of observing through doors, building walls, or around corners. Other townspeople do not block this line of sight.  To determine corners, a straight line is made between the center of the observer's space to the observation space. 
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;Each townsperson able to make an observation attempt may do so only once per turn. Counters that are taken off the mapboard during a take-over cannot observe.&lt;LineBreak/&gt;&lt;LineBreak/&gt;Alien controlled townspeople do not observe Alien take-overs. If the Town player tries to observe with an undiscovered Alien controlled townsperson and succeeds, the Alien player tells the Town player that the townsperson observed nothing because the counter  is actually under Alien control!</t>
+  </si>
+  <si>
+    <t>&lt;Bold&gt;r6.5 Town Player Movement&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+During his or her movement phase, the Town player may move any townsperson that is controlled by the Town player. The Town player may not move uncontrolled townspeople, Alien-controlled townspeople, or townspeople that are:
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+-- Tied Up per &lt;InlineUIContainer&gt;&lt;Button Content='r6.3.2' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt;&lt;LineBreak/&gt;
+-- Unconscious per &lt;InlineUIContainer&gt;&lt;Button Content='Alien Loss' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt;
+ or &lt;InlineUIContainer&gt;&lt;Button Content='Town Loss' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Tables&lt;LineBreak/&gt;
+-- Stunned per Alien Loss or Town Loss Tables &lt;LineBreak/&gt;&lt;LineBreak/&gt;
+An Alien controlled counter in a space may halt or prevent the movement of one Town controlled counter moving into that space. When there is more than one Town-controlled counter to choose from, the Alien player may choose which counters do not move. The decision whether or not to stop a Town controlled counter is made by the Alien player as needed.</t>
+  </si>
+  <si>
+    <t>&lt;Bold&gt;r9.1 Take-Over&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+At the beginning of this phase, the Alien player may remove from the map any group of two counters in the same space neither which is controlled by the Town player.
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+If one of the two counters is Alien controlled and the other is uncontrolled, the Alien player replaces the uncontrolled counter with the duplicate making it an Alien controlled counter. If neither of the removed counters is Alien controlled, the Alien player pretends to exchange them. The Alien player than returns the counters to their original space on the mapboard.
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+&lt;InlineUIContainer&gt;&lt;Button Content='r9.1.1' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Take-over Example&lt;LineBreak/&gt;
+&lt;InlineUIContainer&gt;&lt;Button Content='r9.1.2' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Take-over Restrictions&lt;LineBreak/&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Bold&gt;r7.2.4 Influence - No Effect Causes Skeptic&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+The townsperson did not believe the attempt to convince him or her. That particular townsperson is now highly skeptical about an alien invasion.
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+If an attempt to influence that counter is made again, the Town player must subtract one from the die roll on the &lt;InlineUIContainer&gt;&lt;Button Content='Influence Results' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Table for future attempts. The penalty is not cumulative.</t>
+  </si>
+  <si>
+    <t>&lt;Bold&gt;r8.7.3  Combat - Post Combat Activity - Implant Removal&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+Townspeople are taken-over by Alien controlled counters by means of a bio-mechanical implant attached to the back of the victum's neck. As long as the implant remains attached, that counter remains under the Alien player's control. 
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+The Town player may try to remove this implant from a defeated Alien controlled townsperson, thus breaking the Alien player's control. One Town controlled counter is chosen to attempt the removal. The Town player rolls two dice and consults the 
+&lt;InlineUIContainer&gt;&lt;Button Content='Implant Removal' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Table.
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+Successfully removing the implant causes the victim to come under control of the Town player. If an implant is removed intact, it can be carried as evidence. Such evidence adds +1 to the influence roll when the townsperson carrying the implant tries to influence another townsperson per &lt;InlineUIContainer&gt;&lt;Button Content='r7.2.3' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt;. 
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+As only Alien controlled counters may be interrogated, it is wise to interrogate per &lt;InlineUIContainer&gt;&lt;Button Content='r8.7.2' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt;  before attempting to remove an implant. Removing the implant generates an electric shock which erases all memory of the Alien HQ from the victim's memory, a unique safegard which is built into the implant's circuits.</t>
+  </si>
+  <si>
+    <t>&lt;Bold&gt;r8.6 Combat - Results&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+There are four results that can occur from combat:&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+-- Attacker Flees (AF): Each counter of the Attacker must flee using Random Movement per &lt;InlineUIContainer&gt;&lt;Button Content='r6.3' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt;. If the counter is already in the building, roll again until a different target building is determined. The Alien Sub-Commander cannot flee and instead defeated. Should the Town Player defeat the Sub-Commander, the game is automatically ended with a Town player victory.
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+-- Defender Flees (DF): Same mechanics as Attacker flees but for Defender.
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+-- Attacker Wins (A): Consult the appropriate table: 
+ &lt;InlineUIContainer&gt;&lt;Button Content='Alien Loss' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Table or  
+ &lt;InlineUIContainer&gt;&lt;Button Content='Town Loss' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Table. The dice are rolled for each individual counter of the defeated force, and the results are applied immediately.  Should the Town Player defeat the Sub-Commander, the game is automatically ended with a Town player victory!.
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+-- Defender Wins (D): Same mechanics as Attacker Wins but for Defender.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;Bold&gt;r8.1 Combat - General Rules&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+Combat takes place only between counters sharing the same space. It is not permitted to attack a counter in an adjacent space.
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+All combat is voluntary. Neither player is forced to start combat. Thus, combat takes place only when at least one player desires it.
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+Either player may start combat as desired. Combat for each space is resolved separately and individually. Combat in one area will not affect combat in another area. Each counter may only be involved in one combat per turn.
+</t>
+  </si>
+  <si>
+    <t>&lt;Bold&gt;r9.0 Alien Take-Over, Observation, Wary&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+During this phase, the Alien player may 'take-over' uncontrolled townspeople or stunned controlled Town pieces (but not unconscious), thus bringing them under Alien control. This is handled secretly so the Town player does know know which counters are Alien controlled.
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+&lt;InlineUIContainer&gt;&lt;Button Content='r9.1' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Take-Over&lt;LineBreak/&gt;
+&lt;InlineUIContainer&gt;&lt;Button Content='r9.2' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Observation and Becoming Wary&lt;LineBreak/&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Bold&gt;r7.2 Influencing and Becoming Skeptical&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+The Town player may also try to influence uncontrolled townsperson counters during this phase. 
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+Influencing is trying to convince other townspeople that there is an alien plot afoot to take-over Pleasantville. 
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+This is how the Town player can gain control of additional townspeople. Alien controlled counters cannot influence other counters but take-over townspeople per 
+&lt;InlineUIContainer&gt;&lt;Button Content='r9.1' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt;.
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+&lt;InlineUIContainer&gt;&lt;Button Content='r7.2.1' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Process&lt;LineBreak/&gt;
+&lt;InlineUIContainer&gt;&lt;Button Content='r7.2.2' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Mutliple Town Controlled Counters&lt;LineBreak/&gt;
+&lt;InlineUIContainer&gt;&lt;Button Content='r7.2.3' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Rolling&lt;LineBreak/&gt;
+&lt;InlineUIContainer&gt;&lt;Button Content='r7.2.4' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; No Effect Result  - Becoming Skeptical&lt;LineBreak/&gt;
+&lt;InlineUIContainer&gt;&lt;Button Content='r7.2.5' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Convinced Result&lt;LineBreak/&gt;
+&lt;InlineUIContainer&gt;&lt;Button Content='r7.2.6' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Alien Controlled Counters</t>
+  </si>
+  <si>
+    <t>&lt;Bold&gt;r7.0 Conversation and Influence (Town player only)&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+Conversation and Influence are methods where the Town player interacts with uncontrolled counters to either determine if townsperson is Alien controlled or a way for Town player to recruit additional Town controlled counters.
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+&lt;InlineUIContainer&gt;&lt;Button Content='r7.1' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Conversation&lt;LineBreak/&gt;
+&lt;InlineUIContainer&gt;&lt;Button Content='r7.2' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Influencing and Becoming Skeptical&lt;LineBreak/&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Bold&gt;r8.0 Combat (Tie Up, Interrogation, and Implant Removal)&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
 All combat is resolved in this phase including combat with the Alien controlled counters upon which an influence attempt was made per 
 &lt;InlineUIContainer&gt;&lt;Button Content='r7.2.6' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt;. Both players will resolve combat during this phase of the turn.
 &lt;LineBreak/&gt;&lt;LineBreak/&gt;
@@ -704,88 +758,34 @@
 &lt;InlineUIContainer&gt;&lt;Button Content='r8.4' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Example&lt;LineBreak/&gt;
 &lt;InlineUIContainer&gt;&lt;Button Content='r8.5' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Stacking&lt;LineBreak/&gt;
 &lt;InlineUIContainer&gt;&lt;Button Content='r8.6' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Results&lt;LineBreak/&gt;
-&lt;InlineUIContainer&gt;&lt;Button Content='r8.7' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Post Combat Activity (Town player only)&lt;LineBreak/&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Bold&gt;r8.7 Combat - Post Combat Activity&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-The Town player after winning a combat may choose to do one of the following actions with the defeated Alien controlled counters. These actions are purely voluntary on the part of the Town player, though they can be crucial to the Town player's chances of victory. 
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-Depending on the actual result inflicted upon a defeated Alien controlled counter, some actions may not always be possible (e.g., interrogating a dead or knocked-out piece). The  &lt;InlineUIContainer&gt;&lt;Button Content='Alien Loss' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Table specifies which actions may be taken in each given circumstances.
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-Post Combat Activities are the following:&lt;LineBreak/&gt;
-&lt;InlineUIContainer&gt;&lt;Button Content='r8.7.1' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Tie Up&lt;LineBreak/&gt;
-&lt;InlineUIContainer&gt;&lt;Button Content='r8.7.2' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Interrogation&lt;LineBreak/&gt;
-&lt;InlineUIContainer&gt;&lt;Button Content='r8.7.3' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Implant Removal&lt;LineBreak/&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Bold&gt;r9.2.2 Observation Restrictions&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-Observation cannot take place more than 3 spaces away. Observations are blocked by corners and walls. Townspeople have no chance of observing through doors, building walls, or around corners. Other townspeople do not block this line of sight.  To determine corners, a straight line is made between the center of the observer's space to the observation space. 
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;Each townsperson able to make an observation attempt may do so only once per turn. Counters that are taken off the mapboard during a take-over cannot observe.&lt;LineBreak/&gt;&lt;LineBreak/&gt;Alien controlled townspeople do not observe Alien take-overs. If the Town player tries to observe with an undiscovered Alien controlled townsperson and succeeds, the Alien player tells the Town player that the townsperson observed nothing because the counter  is actually under Alien control!</t>
-  </si>
-  <si>
-    <t>&lt;Bold&gt;r6.5 Town Player Movement&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-During his or her movement phase, the Town player may move any townsperson that is controlled by the Town player. The Town player may not move uncontrolled townspeople, Alien-controlled townspeople, or townspeople that are:
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
--- Tied Up per &lt;InlineUIContainer&gt;&lt;Button Content='r6.3.2' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt;&lt;LineBreak/&gt;
--- Unconscious per &lt;InlineUIContainer&gt;&lt;Button Content='Alien Loss' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt;
- or &lt;InlineUIContainer&gt;&lt;Button Content='Town Loss' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Tables&lt;LineBreak/&gt;
--- Stunned per Alien Loss or Town Loss Tables &lt;LineBreak/&gt;&lt;LineBreak/&gt;
-An Alien controlled counter in a space may halt or prevent the movement of one Town controlled counter moving into that space. When there is more than one Town-controlled counter to choose from, the Alien player may choose which counters do not move. The decision whether or not to stop a Town controlled counter is made by the Alien player as needed.</t>
-  </si>
-  <si>
-    <t>&lt;Bold&gt;r9.1 Take-Over&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-At the beginning of this phase, the Alien player may remove from the map any group of two counters in the same space neither which is controlled by the Town player.
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-If one of the two counters is Alien controlled and the other is uncontrolled, the Alien player replaces the uncontrolled counter with the duplicate making it an Alien controlled counter. If neither of the removed counters is Alien controlled, the Alien player pretends to exchange them. The Alien player than returns the counters to their original space on the mapboard.
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-&lt;InlineUIContainer&gt;&lt;Button Content='r9.1.1' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Take-over Example&lt;LineBreak/&gt;
-&lt;InlineUIContainer&gt;&lt;Button Content='r9.1.2' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Take-over Restrictions&lt;LineBreak/&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Bold&gt;r7.2.4 Influence - No Effect Causes Skeptic&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-The townsperson did not believe the attempt to convince him or her. That particular townsperson is now highly skeptical about an alien invasion.
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-If an attempt to influence that counter is made again, the Town player must subtract one from the die roll on the &lt;InlineUIContainer&gt;&lt;Button Content='Influence Results' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Table for future attempts. The penalty is not cumulative.</t>
-  </si>
-  <si>
-    <t>&lt;Bold&gt;r8.7.3  Combat - Post Combat Activity - Implant Removal&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-Townspeople are taken-over by Alien controlled counters by means of a bio-mechanical implant attached to the back of the victum's neck. As long as the implant remains attached, that counter remains under the Alien player's control. 
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-The Town player may try to remove this implant from a defeated Alien controlled townsperson, thus breaking the Alien player's control. One Town controlled counter is chosen to attempt the removal. The Town player rolls two dice and consults the 
-&lt;InlineUIContainer&gt;&lt;Button Content='Implant Removal' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Table.
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-Successfully removing the implant causes the victim to come under control of the Town player. If an implant is removed intact, it can be carried as evidence. Such evidence adds +1 to the influence roll when the townsperson carrying the implant tries to influence another townsperson per &lt;InlineUIContainer&gt;&lt;Button Content='r7.2.3' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt;. 
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-As only Alien controlled counters may be interrogated, it is wise to interrogate per &lt;InlineUIContainer&gt;&lt;Button Content='r8.7.2' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt;  before attempting to remove an implant. Removing the implant generates an electric shock which erases all memory of the Alien HQ from the victim's memory, a unique safegard which is built into the implant's circuits.</t>
-  </si>
-  <si>
-    <t>&lt;Bold&gt;r9.0 Alien Take-Over And Observation&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-During this phase, the Alien player may 'take-over' uncontrolled townspeople or stunned controlled Town pieces (but not unconscious), thus bringing them under Alien control. This is handled secretly so the Town player does know know which counters are Alien controlled.
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-&lt;InlineUIContainer&gt;&lt;Button Content='r9.1' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Take-Over&lt;LineBreak/&gt;
-&lt;InlineUIContainer&gt;&lt;Button Content='r9.2' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Observation&lt;LineBreak/&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Bold&gt;r8.6 Combat - Results&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-There are four results that can occur from combat:&lt;LineBreak/&gt;&lt;LineBreak/&gt;
--- Attacker Flees (AF): Each counter of the Attacker must flee using Random Movement per &lt;InlineUIContainer&gt;&lt;Button Content='r6.3' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt;. If the counter is already in the building, roll again until a different target building is determined. The Alien Sub-Commander cannot flee and instead defeated. Should the Town Player defeat the Sub-Commander, the game is automatically ended with a Town player victory.
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
--- Defender Flees (DF): Same mechanics as Attacker flees but for Defender.
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
--- Attacker Wins (A): Consult the appropriate table: 
- &lt;InlineUIContainer&gt;&lt;Button Content='Alien Loss' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Table or  
- &lt;InlineUIContainer&gt;&lt;Button Content='Town Loss' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Table. The dice are rolled for each individual counter of the defeated force, and the results are applied immediately.  Should the Town Player defeat the Sub-Commander, the game is automatically ended with a Town player victory!.
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
--- Defender Wins (D): Same mechanics as Attacker Wins but for Defender.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;Bold&gt;r8.1 Combat - General Rules&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-Combat takes place only between counters sharing the same space. It is not permitted to attack a counter in an adjacent space.
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-All combat is voluntary. Neither player is forced to start combat. Thus, combat takes place only when at least one player desires it.
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;
-Either player may start combat as desired. Combat for each space is resolved separately and individually. Combat in one area will not affect combat in another area. Each counter may only be involved in one combat per turn.
-</t>
+&lt;InlineUIContainer&gt;&lt;Button Content='r8.7' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Post Combat Activity (Tie Up, Interrogation, and Implant Removal)&lt;LineBreak/&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Bold&gt;r9.2.1 Becoming Wary&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+If the observation attempt is successful, the Town player may flip over one of the observed counters to see if it is Alien controlled. If an Alien controlled counter is discovered, and the observing townsperson is currently uncontrolled, the counter has observed a take-over. 
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+The observing counter is still uncontrolled but wary.
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+A town player who tries to influence a wary person gains a +1 on his or her dice roll on the 
+&lt;InlineUIContainer&gt;&lt;Button Content='Influence Result' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt; &lt;/InlineUIContainer&gt; Table per 
+&lt;InlineUIContainer&gt;&lt;Button Content='r7.2.3' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; because that townsperson has already witnessed some funny business which makes this suspicious.
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+In addition, that townsperson is now somewhat alert to a take-over attempt, lest the same thing happen to him or her, and may not be moved or taken-over outright by the Alien player for the remainder of the game. This counter must be attacked and defeated by the Alien player before the Alien player moves it or tries to take-over it again per Combat per 
+&lt;InlineUIContainer&gt;&lt;Button Content='r7.2.3' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt;.. 
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+If the Alien player is defeated in an attack on the wary townsperson, the result is an automatic flee result for the Alien controlled counters involved per 
+&lt;InlineUIContainer&gt;&lt;Button Content='r8.6' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt;.</t>
+  </si>
+  <si>
+    <t>&lt;Bold&gt;r9.2 Take-over Observation (Becoming Wary)&lt;/Bold&gt;&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+There is a chance that a nearby townsperson will watch closely enough to detect an Alien take-over if one occurs. 
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+Any time the Alien player removes counters from the mapboard during a take-over, a townsperson might notice or observe the take-over. 
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+Refer to the &lt;InlineUIContainer&gt;&lt;Button Content='Observation' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Table which gives the number that must be rolled on one die for a townsperson to successfully observe a take-over based on the townsperson location to the observation space.
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;
+&lt;InlineUIContainer&gt;&lt;Button Content='r9.2.1' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Becoming Wary&lt;LineBreak/&gt;
+&lt;InlineUIContainer&gt;&lt;Button Content='r9.2.2' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt; Observation Restrictions&lt;LineBreak/&gt;</t>
   </si>
 </sst>
 </file>
@@ -1167,7 +1167,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="240" x14ac:dyDescent="0.25">
@@ -1215,7 +1215,7 @@
         <v>27</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -1279,7 +1279,7 @@
         <v>34</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -1287,7 +1287,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -1295,7 +1295,7 @@
         <v>36</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -1367,7 +1367,7 @@
         <v>12</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -1391,7 +1391,7 @@
         <v>39</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="270" x14ac:dyDescent="0.25">
@@ -1407,7 +1407,7 @@
         <v>41</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -1415,7 +1415,7 @@
         <v>2</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -1423,7 +1423,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="210" x14ac:dyDescent="0.25">
@@ -1431,7 +1431,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -1439,7 +1439,7 @@
         <v>43</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -1447,7 +1447,7 @@
         <v>44</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -1463,7 +1463,7 @@
         <v>46</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -1487,7 +1487,7 @@
         <v>16</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -1495,7 +1495,7 @@
         <v>17</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="225" x14ac:dyDescent="0.25">
@@ -1503,7 +1503,7 @@
         <v>18</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="132.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1519,7 +1519,7 @@
         <v>50</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -1535,7 +1535,7 @@
         <v>21</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -1543,7 +1543,7 @@
         <v>51</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -1551,7 +1551,7 @@
         <v>84</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -1567,7 +1567,7 @@
         <v>85</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -1575,7 +1575,7 @@
         <v>22</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -1583,7 +1583,7 @@
         <v>23</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -1599,7 +1599,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -1607,7 +1607,7 @@
         <v>24</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="240" x14ac:dyDescent="0.25">
@@ -1615,7 +1615,7 @@
         <v>54</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -1623,7 +1623,7 @@
         <v>55</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
